--- a/docs/Milestone/CST-452_Traceability_Matrix_SecureLink.xlsx
+++ b/docs/Milestone/CST-452_Traceability_Matrix_SecureLink.xlsx
@@ -1546,7 +1546,7 @@
       <c r="H21" s="79" t="n"/>
       <c r="I21" s="80" t="n"/>
     </row>
-    <row r="22" ht="45" customHeight="1" s="72">
+    <row r="22" ht="75" customHeight="1" s="72">
       <c r="A22" s="85" t="inlineStr">
         <is>
           <t>018</t>
@@ -1560,28 +1560,28 @@
       </c>
       <c r="D22" s="82" t="inlineStr">
         <is>
-          <t>Not yet designed</t>
+          <t>TokenStore.cs and ApiClient.cs class comments; Requirements Review</t>
         </is>
       </c>
       <c r="E22" s="83" t="inlineStr">
         <is>
-          <t>ApiClient.AuthToken (TODO Phase 4)</t>
+          <t>TokenStore (Windows Credential Manager); ApiClient.TryRestoreSessionAsync() / RefreshTokenAsync() / SignOut(); AuthController.Refresh()</t>
         </is>
       </c>
       <c r="F22" s="84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TC-AUTH-07, TC-AUTH-08, TC-AUTH-09, TC-AUTH-10</t>
         </is>
       </c>
       <c r="G22" s="78" t="inlineStr">
         <is>
-          <t>Not implemented yet — currently an in-memory field only. Planned for a later milestone. Out of scope for Milestone 5 testing; planned for Milestone 6.</t>
+          <t>Completed in Milestone 6. Token is saved on sign-in, restored and refreshed on launch, and removed on Sign out. The refresh endpoint also keeps long sessions signed in.</t>
         </is>
       </c>
       <c r="H22" s="79" t="n"/>
       <c r="I22" s="80" t="n"/>
     </row>
-    <row r="23" ht="45" customHeight="1" s="72">
+    <row r="23" ht="75" customHeight="1" s="72">
       <c r="A23" s="85" t="inlineStr">
         <is>
           <t>019</t>
@@ -1595,22 +1595,22 @@
       </c>
       <c r="D23" s="82" t="inlineStr">
         <is>
-          <t>Not yet designed</t>
+          <t>TunnelHealth.cs class comment; Requirements Review</t>
         </is>
       </c>
       <c r="E23" s="83" t="inlineStr">
         <is>
-          <t>WireGuardInterop.IsHandshakeActive() (TODO Phase 5 / HealthMonitor)</t>
+          <t>WireGuardInterop.GetLatestHandshakeUtc(); TunnelHealth.Evaluate(); MainWindow.CheckTunnelHealth()</t>
         </is>
       </c>
       <c r="F23" s="84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TC-WG-07, TC-WG-08</t>
         </is>
       </c>
       <c r="G23" s="78" t="inlineStr">
         <is>
-          <t>Stub only — checks for "any output," doesn't yet compare timestamps or surface an alert. Out of scope for Milestone 5 testing; planned for Milestone 6.</t>
+          <t>Completed in Milestone 6. Checked every 5 s while connected; shows "Connection lost" when the last handshake is older than 180 s and clears when the relay answers again.</t>
         </is>
       </c>
       <c r="H23" s="79" t="n"/>
